--- a/Output/Final/Validation-Individual.xlsx
+++ b/Output/Final/Validation-Individual.xlsx
@@ -467,7 +467,7 @@
         <v>236</v>
       </c>
       <c r="E2" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -476,25 +476,25 @@
         <v>16</v>
       </c>
       <c r="H2" t="n">
-        <v>1929.00255461163</v>
+        <v>1929.00248042274</v>
       </c>
       <c r="I2" t="n">
-        <v>1897.06222682173</v>
+        <v>1897.06213437811</v>
       </c>
       <c r="J2" t="n">
-        <v>-11.0990681765971</v>
+        <v>-11.0990721266398</v>
       </c>
       <c r="K2" t="n">
-        <v>11.0990681765971</v>
+        <v>11.0990721266398</v>
       </c>
       <c r="L2" t="n">
-        <v>0.024890305861215</v>
+        <v>0.025125430697482</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0326678346531996</v>
+        <v>0.0329862920789466</v>
       </c>
       <c r="N2" t="n">
-        <v>0.178436511596538</v>
+        <v>0.00998560123619926</v>
       </c>
     </row>
     <row r="3">
@@ -511,7 +511,7 @@
         <v>236</v>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -520,25 +520,25 @@
         <v>18</v>
       </c>
       <c r="H3" t="n">
-        <v>-116358.962252481</v>
+        <v>-116358.962253079</v>
       </c>
       <c r="I3" t="n">
-        <v>1295288.55066242</v>
+        <v>1295288.55049816</v>
       </c>
       <c r="J3" t="n">
-        <v>-160.609561630847</v>
+        <v>-160.609561462601</v>
       </c>
       <c r="K3" t="n">
-        <v>160.609561630847</v>
+        <v>160.609561462601</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0286650332671136</v>
+        <v>0.0286617557055946</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0413586404500581</v>
+        <v>0.0413521095146867</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0952492342728489</v>
+        <v>0.0952420008298979</v>
       </c>
     </row>
     <row r="4">
@@ -555,7 +555,7 @@
         <v>236</v>
       </c>
       <c r="E4" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
@@ -564,25 +564,25 @@
         <v>18</v>
       </c>
       <c r="H4" t="n">
-        <v>1930.69966049625</v>
+        <v>1930.70015225405</v>
       </c>
       <c r="I4" t="n">
-        <v>1900.18266833313</v>
+        <v>1900.1833305034</v>
       </c>
       <c r="J4" t="n">
-        <v>-11.0672805852303</v>
+        <v>-11.0672568147778</v>
       </c>
       <c r="K4" t="n">
-        <v>11.0672805852303</v>
+        <v>11.0672568147778</v>
       </c>
       <c r="L4" t="n">
-        <v>0.024863118059087</v>
+        <v>0.0249195754849078</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0315269534336837</v>
+        <v>0.0317300958618918</v>
       </c>
       <c r="N4" t="n">
-        <v>0.305795832412785</v>
+        <v>0.289216817479002</v>
       </c>
     </row>
     <row r="5">
@@ -599,7 +599,7 @@
         <v>236</v>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="F5" t="n">
         <v>6</v>
@@ -608,25 +608,25 @@
         <v>18</v>
       </c>
       <c r="H5" t="n">
-        <v>1915.79519054529</v>
+        <v>1915.79517877502</v>
       </c>
       <c r="I5" t="n">
-        <v>1876.99160396389</v>
+        <v>1876.99160186951</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.36018174070436</v>
+        <v>-9.36017634559116</v>
       </c>
       <c r="K5" t="n">
-        <v>9.36018174070436</v>
+        <v>9.36017634559116</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0155913259977085</v>
+        <v>0.015758726017285</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0248062937625489</v>
+        <v>0.02495474549407</v>
       </c>
       <c r="N5" t="n">
-        <v>0.660870136772157</v>
+        <v>0.656003091397798</v>
       </c>
     </row>
     <row r="6">
@@ -643,7 +643,7 @@
         <v>236</v>
       </c>
       <c r="E6" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -652,25 +652,25 @@
         <v>16</v>
       </c>
       <c r="H6" t="n">
-        <v>1916.42799513853</v>
+        <v>1916.42799365217</v>
       </c>
       <c r="I6" t="n">
-        <v>1878.09825428041</v>
+        <v>1878.09825283184</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.32095930672482</v>
+        <v>-9.3209595274152</v>
       </c>
       <c r="K6" t="n">
-        <v>9.32095930672482</v>
+        <v>9.3209595274152</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0153293546180437</v>
+        <v>0.0152983521235951</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0244345773206554</v>
+        <v>0.0246774020590179</v>
       </c>
       <c r="N6" t="n">
-        <v>0.673936191283028</v>
+        <v>0.664119577310393</v>
       </c>
     </row>
     <row r="7">
@@ -687,7 +687,7 @@
         <v>236</v>
       </c>
       <c r="E7" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -708,13 +708,13 @@
         <v>11.1969232344632</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0638038472500594</v>
+        <v>0.0628138975561198</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0762134520487924</v>
+        <v>0.0751670614777191</v>
       </c>
       <c r="N7" t="n">
-        <v>0.161591514865081</v>
+        <v>0.187668749379659</v>
       </c>
     </row>
     <row r="8">
@@ -731,7 +731,7 @@
         <v>236</v>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -740,25 +740,25 @@
         <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>1956.60444245831</v>
+        <v>1956.60446590393</v>
       </c>
       <c r="I8" t="n">
-        <v>1919.87941771174</v>
+        <v>1919.87944774133</v>
       </c>
       <c r="J8" t="n">
-        <v>-10.5856950206343</v>
+        <v>-10.5856936289614</v>
       </c>
       <c r="K8" t="n">
-        <v>10.5856950206343</v>
+        <v>10.5856936289614</v>
       </c>
       <c r="L8" t="n">
-        <v>0.023303266317161</v>
+        <v>0.0229521648389245</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0275803510863162</v>
+        <v>0.0275521699710453</v>
       </c>
       <c r="N8" t="n">
-        <v>0.116649834659887</v>
+        <v>0.0056562809572386</v>
       </c>
     </row>
     <row r="9">
@@ -775,7 +775,7 @@
         <v>236</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
@@ -784,25 +784,25 @@
         <v>18</v>
       </c>
       <c r="H9" t="n">
-        <v>-112012.508978697</v>
+        <v>-112012.508979294</v>
       </c>
       <c r="I9" t="n">
-        <v>893188.162768309</v>
+        <v>893188.162535294</v>
       </c>
       <c r="J9" t="n">
-        <v>-143.276489894499</v>
+        <v>-143.276489841089</v>
       </c>
       <c r="K9" t="n">
-        <v>143.276489894499</v>
+        <v>143.276489841089</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0256883006306533</v>
+        <v>0.0256910739125687</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0354727743221341</v>
+        <v>0.0354775060895288</v>
       </c>
       <c r="N9" t="n">
-        <v>0.150003000525701</v>
+        <v>0.149983668227869</v>
       </c>
     </row>
     <row r="10">
@@ -819,7 +819,7 @@
         <v>236</v>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="F10" t="n">
         <v>6</v>
@@ -828,25 +828,25 @@
         <v>18</v>
       </c>
       <c r="H10" t="n">
-        <v>1959.18128447957</v>
+        <v>1959.18128420318</v>
       </c>
       <c r="I10" t="n">
-        <v>1924.70594498904</v>
+        <v>1924.70594496655</v>
       </c>
       <c r="J10" t="n">
-        <v>-10.4705428962063</v>
+        <v>-10.4705428500662</v>
       </c>
       <c r="K10" t="n">
-        <v>10.4705428962063</v>
+        <v>10.4705428500662</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0244188846727486</v>
+        <v>0.024814544477274</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0289409160820772</v>
+        <v>0.0292415430262749</v>
       </c>
       <c r="N10" t="n">
-        <v>0.136129883979147</v>
+        <v>0.119964780102735</v>
       </c>
     </row>
     <row r="11">
@@ -863,7 +863,7 @@
         <v>236</v>
       </c>
       <c r="E11" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="F11" t="n">
         <v>6</v>
@@ -872,25 +872,25 @@
         <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>1944.49436819276</v>
+        <v>1944.49431746606</v>
       </c>
       <c r="I11" t="n">
-        <v>1902.31574087907</v>
+        <v>1902.31562008279</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.35714522464203</v>
+        <v>-9.35715465375013</v>
       </c>
       <c r="K11" t="n">
-        <v>9.35714522464203</v>
+        <v>9.35715465375013</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0149735619980506</v>
+        <v>0.0151707440970892</v>
       </c>
       <c r="M11" t="n">
-        <v>0.019091048691247</v>
+        <v>0.0193211270356685</v>
       </c>
       <c r="N11" t="n">
-        <v>0.72799874067993</v>
+        <v>0.722258349330749</v>
       </c>
     </row>
     <row r="12">
@@ -907,7 +907,7 @@
         <v>236</v>
       </c>
       <c r="E12" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -916,25 +916,25 @@
         <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>1944.81247032401</v>
+        <v>1944.81250228062</v>
       </c>
       <c r="I12" t="n">
-        <v>1902.85736561949</v>
+        <v>1902.85737925445</v>
       </c>
       <c r="J12" t="n">
-        <v>-9.29533595157938</v>
+        <v>-9.29533800940576</v>
       </c>
       <c r="K12" t="n">
-        <v>9.29533595157938</v>
+        <v>9.29533800940576</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0143430219912846</v>
+        <v>0.0143021422669668</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0183415757406858</v>
+        <v>0.0183596736470922</v>
       </c>
       <c r="N12" t="n">
-        <v>0.745025558131644</v>
+        <v>0.745459056343812</v>
       </c>
     </row>
     <row r="13">
@@ -951,7 +951,7 @@
         <v>236</v>
       </c>
       <c r="E13" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -960,25 +960,25 @@
         <v>16</v>
       </c>
       <c r="H13" t="n">
-        <v>268.514397908745</v>
+        <v>268.514369025366</v>
       </c>
       <c r="I13" t="n">
-        <v>3748.86477250848</v>
+        <v>3748.86457986811</v>
       </c>
       <c r="J13" t="n">
-        <v>-12.4652822650036</v>
+        <v>-12.4652824336078</v>
       </c>
       <c r="K13" t="n">
-        <v>12.4652822650036</v>
+        <v>12.4652824336078</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0842653392930719</v>
+        <v>0.0847030037780895</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0949631699723956</v>
+        <v>0.0956827055295294</v>
       </c>
       <c r="N13" t="n">
-        <v>0.336517199443956</v>
+        <v>0.297098133223336</v>
       </c>
     </row>
     <row r="14">
@@ -995,7 +995,7 @@
         <v>238</v>
       </c>
       <c r="E14" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1016,13 +1016,13 @@
         <v>10.7665380665202</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0226959273338774</v>
+        <v>0.0226645892024139</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0313253780053738</v>
+        <v>0.030960789711795</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.163129712885762</v>
+        <v>0.0610594573372275</v>
       </c>
     </row>
     <row r="15">
@@ -1039,7 +1039,7 @@
         <v>238</v>
       </c>
       <c r="E15" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="F15" t="n">
         <v>6</v>
@@ -1048,25 +1048,25 @@
         <v>18</v>
       </c>
       <c r="H15" t="n">
-        <v>-131157.681674291</v>
+        <v>-131157.681676007</v>
       </c>
       <c r="I15" t="n">
-        <v>399751.831524367</v>
+        <v>399751.831285122</v>
       </c>
       <c r="J15" t="n">
-        <v>-153.89037207373</v>
+        <v>-153.890371839386</v>
       </c>
       <c r="K15" t="n">
-        <v>153.89037207373</v>
+        <v>153.890371839386</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0252148822218696</v>
+        <v>0.0252169971065029</v>
       </c>
       <c r="M15" t="n">
-        <v>0.03558752063702</v>
+        <v>0.0355908547683357</v>
       </c>
       <c r="N15" t="n">
-        <v>0.156137640088681</v>
+        <v>0.156099147503149</v>
       </c>
     </row>
     <row r="16">
@@ -1083,7 +1083,7 @@
         <v>238</v>
       </c>
       <c r="E16" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="F16" t="n">
         <v>6</v>
@@ -1092,25 +1092,25 @@
         <v>18</v>
       </c>
       <c r="H16" t="n">
-        <v>1962.19759247896</v>
+        <v>1962.19759081175</v>
       </c>
       <c r="I16" t="n">
-        <v>1927.93198673552</v>
+        <v>1927.93198381375</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.6437159709792</v>
+        <v>-10.6437157473978</v>
       </c>
       <c r="K16" t="n">
-        <v>10.6437159709792</v>
+        <v>10.6437157473978</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0258062237738954</v>
+        <v>0.0257665922450675</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0335746708742756</v>
+        <v>0.0336042542540761</v>
       </c>
       <c r="N16" t="n">
-        <v>0.00692437746976027</v>
+        <v>0.0262780028796637</v>
       </c>
     </row>
     <row r="17">
@@ -1127,7 +1127,7 @@
         <v>238</v>
       </c>
       <c r="E17" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="F17" t="n">
         <v>6</v>
@@ -1136,25 +1136,25 @@
         <v>18</v>
       </c>
       <c r="H17" t="n">
-        <v>1945.14651752604</v>
+        <v>1945.14654004108</v>
       </c>
       <c r="I17" t="n">
-        <v>1902.078669518</v>
+        <v>1902.07874557206</v>
       </c>
       <c r="J17" t="n">
-        <v>-8.51359026714132</v>
+        <v>-8.51358712635853</v>
       </c>
       <c r="K17" t="n">
-        <v>8.51359026714132</v>
+        <v>8.51358712635853</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0177662654214832</v>
+        <v>0.018206200246875</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0319939076164524</v>
+        <v>0.0324160158092093</v>
       </c>
       <c r="N17" t="n">
-        <v>0.371888817224763</v>
+        <v>0.365397099953357</v>
       </c>
     </row>
     <row r="18">
@@ -1171,7 +1171,7 @@
         <v>238</v>
       </c>
       <c r="E18" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1180,25 +1180,25 @@
         <v>16</v>
       </c>
       <c r="H18" t="n">
-        <v>1944.80669898964</v>
+        <v>1944.80671958829</v>
       </c>
       <c r="I18" t="n">
-        <v>1901.8758884871</v>
+        <v>1901.87594900046</v>
       </c>
       <c r="J18" t="n">
-        <v>-8.41220019714615</v>
+        <v>-8.41219412037954</v>
       </c>
       <c r="K18" t="n">
-        <v>8.41220019714615</v>
+        <v>8.41219412037954</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0170465706287061</v>
+        <v>0.0172786255226406</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0304867451199393</v>
+        <v>0.0306789342376951</v>
       </c>
       <c r="N18" t="n">
-        <v>0.404949154859241</v>
+        <v>0.400402507820406</v>
       </c>
     </row>
     <row r="19">
@@ -1215,7 +1215,7 @@
         <v>238</v>
       </c>
       <c r="E19" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1236,13 +1236,13 @@
         <v>10.5530979875955</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0207969113349304</v>
+        <v>0.0206490333652647</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0326563397342887</v>
+        <v>0.0327310448235158</v>
       </c>
       <c r="N19" t="n">
-        <v>0.276491444968343</v>
+        <v>0.275527297211924</v>
       </c>
     </row>
     <row r="20">
@@ -1259,7 +1259,7 @@
         <v>240</v>
       </c>
       <c r="E20" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1280,13 +1280,13 @@
         <v>10.7451485441314</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0184578695308413</v>
+        <v>0.0188870622413511</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0234230717837085</v>
+        <v>0.0239220517970768</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0251529537884686</v>
+        <v>-0.222583573907048</v>
       </c>
     </row>
     <row r="21">
@@ -1303,7 +1303,7 @@
         <v>240</v>
       </c>
       <c r="E21" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
         <v>6</v>
@@ -1312,25 +1312,25 @@
         <v>18</v>
       </c>
       <c r="H21" t="n">
-        <v>-149065.664694933</v>
+        <v>-149065.664695628</v>
       </c>
       <c r="I21" t="n">
-        <v>1296533.00626416</v>
+        <v>1296533.00604999</v>
       </c>
       <c r="J21" t="n">
-        <v>-163.422229133583</v>
+        <v>-163.422229127639</v>
       </c>
       <c r="K21" t="n">
-        <v>163.422229133583</v>
+        <v>163.422229127639</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0215785812995102</v>
+        <v>0.0215812772159155</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0292562604956581</v>
+        <v>0.0292611095631228</v>
       </c>
       <c r="N21" t="n">
-        <v>0.24857809828682</v>
+        <v>0.248575806854223</v>
       </c>
     </row>
     <row r="22">
@@ -1347,7 +1347,7 @@
         <v>240</v>
       </c>
       <c r="E22" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="F22" t="n">
         <v>6</v>
@@ -1356,25 +1356,25 @@
         <v>18</v>
       </c>
       <c r="H22" t="n">
-        <v>2000.89170858992</v>
+        <v>2000.89173555189</v>
       </c>
       <c r="I22" t="n">
-        <v>1968.57724501549</v>
+        <v>1968.57727995534</v>
       </c>
       <c r="J22" t="n">
-        <v>-10.6735343588727</v>
+        <v>-10.6735329286466</v>
       </c>
       <c r="K22" t="n">
-        <v>10.6735343588727</v>
+        <v>10.6735329286466</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0197605561354667</v>
+        <v>0.0197753324505749</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0239748316001246</v>
+        <v>0.0237074996499752</v>
       </c>
       <c r="N22" t="n">
-        <v>0.198576745684399</v>
+        <v>0.219535631642464</v>
       </c>
     </row>
     <row r="23">
@@ -1391,7 +1391,7 @@
         <v>240</v>
       </c>
       <c r="E23" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="F23" t="n">
         <v>6</v>
@@ -1400,25 +1400,25 @@
         <v>18</v>
       </c>
       <c r="H23" t="n">
-        <v>1980.42020921915</v>
+        <v>1980.42024247131</v>
       </c>
       <c r="I23" t="n">
-        <v>1935.89970151006</v>
+        <v>1935.89976650161</v>
       </c>
       <c r="J23" t="n">
-        <v>-9.17106076059604</v>
+        <v>-9.17105697582416</v>
       </c>
       <c r="K23" t="n">
-        <v>9.17106076059604</v>
+        <v>9.17105697582416</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0147366997515099</v>
+        <v>0.0145864583732407</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0198688445233409</v>
+        <v>0.0196008673924456</v>
       </c>
       <c r="N23" t="n">
-        <v>0.608707734829185</v>
+        <v>0.623326496654269</v>
       </c>
     </row>
     <row r="24">
@@ -1435,7 +1435,7 @@
         <v>240</v>
       </c>
       <c r="E24" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1444,25 +1444,25 @@
         <v>16</v>
       </c>
       <c r="H24" t="n">
-        <v>1980.70131690714</v>
+        <v>1980.70132817114</v>
       </c>
       <c r="I24" t="n">
-        <v>1936.26591351985</v>
+        <v>1936.26595375718</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.14218084252003</v>
+        <v>-9.14217425921067</v>
       </c>
       <c r="K24" t="n">
-        <v>9.14218084252003</v>
+        <v>9.14217425921067</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0143951169927849</v>
+        <v>0.0144845093564029</v>
       </c>
       <c r="M24" t="n">
-        <v>0.019683136848206</v>
+        <v>0.0199271271353379</v>
       </c>
       <c r="N24" t="n">
-        <v>0.607734140952168</v>
+        <v>0.597447571547527</v>
       </c>
     </row>
     <row r="25">
@@ -1479,7 +1479,7 @@
         <v>240</v>
       </c>
       <c r="E25" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1488,25 +1488,25 @@
         <v>16</v>
       </c>
       <c r="H25" t="n">
-        <v>1624.57464308897</v>
+        <v>1624.57466311634</v>
       </c>
       <c r="I25" t="n">
-        <v>3475.00034194227</v>
+        <v>3475.00067287248</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.4356068244049</v>
+        <v>-11.4356067075586</v>
       </c>
       <c r="K25" t="n">
-        <v>11.4356068244049</v>
+        <v>11.4356067075586</v>
       </c>
       <c r="L25" t="n">
-        <v>0.119458870813955</v>
+        <v>0.120208536771114</v>
       </c>
       <c r="M25" t="n">
-        <v>0.165701491712205</v>
+        <v>0.165658127288723</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.118453004051723</v>
+        <v>-0.105476650189209</v>
       </c>
     </row>
     <row r="26">
@@ -1523,7 +1523,7 @@
         <v>241</v>
       </c>
       <c r="E26" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1532,25 +1532,25 @@
         <v>16</v>
       </c>
       <c r="H26" t="n">
-        <v>2007.13071089605</v>
+        <v>2007.13072302271</v>
       </c>
       <c r="I26" t="n">
-        <v>1973.7432811416</v>
+        <v>1973.74329544237</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.7254547675122</v>
+        <v>-10.7254542109487</v>
       </c>
       <c r="K26" t="n">
-        <v>10.7254547675122</v>
+        <v>10.7254542109487</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0253680340170783</v>
+        <v>0.0253150849870043</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0329986178461853</v>
+        <v>0.0333134179022128</v>
       </c>
       <c r="N26" t="n">
-        <v>0.2290799335186</v>
+        <v>0.0383806556064346</v>
       </c>
     </row>
     <row r="27">
@@ -1567,7 +1567,7 @@
         <v>241</v>
       </c>
       <c r="E27" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="F27" t="n">
         <v>6</v>
@@ -1576,25 +1576,25 @@
         <v>18</v>
       </c>
       <c r="H27" t="n">
-        <v>-142358.250624654</v>
+        <v>-142358.250624037</v>
       </c>
       <c r="I27" t="n">
-        <v>943946.6229567</v>
+        <v>943946.62303646</v>
       </c>
       <c r="J27" t="n">
-        <v>-161.664123493863</v>
+        <v>-161.664123566907</v>
       </c>
       <c r="K27" t="n">
-        <v>161.664123493863</v>
+        <v>161.664123566907</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0321759534270648</v>
+        <v>0.0321748373092391</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0448029823322922</v>
+        <v>0.0448030774707229</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.0691263501997657</v>
+        <v>-0.0691512711606316</v>
       </c>
     </row>
     <row r="28">
@@ -1611,7 +1611,7 @@
         <v>241</v>
       </c>
       <c r="E28" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="F28" t="n">
         <v>6</v>
@@ -1620,25 +1620,25 @@
         <v>18</v>
       </c>
       <c r="H28" t="n">
-        <v>2008.8318091105</v>
+        <v>2008.8318245455</v>
       </c>
       <c r="I28" t="n">
-        <v>1977.03761852136</v>
+        <v>1977.03763574742</v>
       </c>
       <c r="J28" t="n">
-        <v>-10.6772300217206</v>
+        <v>-10.6772299092037</v>
       </c>
       <c r="K28" t="n">
-        <v>10.6772300217206</v>
+        <v>10.6772299092037</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0251493555109231</v>
+        <v>0.0250790752695115</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0321300896367763</v>
+        <v>0.0320677698931033</v>
       </c>
       <c r="N28" t="n">
-        <v>0.277298870605691</v>
+        <v>0.284035245322339</v>
       </c>
     </row>
     <row r="29">
@@ -1655,7 +1655,7 @@
         <v>241</v>
       </c>
       <c r="E29" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="F29" t="n">
         <v>6</v>
@@ -1664,25 +1664,25 @@
         <v>18</v>
       </c>
       <c r="H29" t="n">
-        <v>1987.1146227763</v>
+        <v>1987.11478595052</v>
       </c>
       <c r="I29" t="n">
-        <v>1944.24569638794</v>
+        <v>1944.24592121554</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.79491709300186</v>
+        <v>-8.79491932310068</v>
       </c>
       <c r="K29" t="n">
-        <v>8.79491709300186</v>
+        <v>8.79491932310068</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0166288721053309</v>
+        <v>0.0167118638726498</v>
       </c>
       <c r="M29" t="n">
-        <v>0.026068608846201</v>
+        <v>0.0260664179284159</v>
       </c>
       <c r="N29" t="n">
-        <v>0.615769466322632</v>
+        <v>0.615912583234676</v>
       </c>
     </row>
     <row r="30">
@@ -1699,7 +1699,7 @@
         <v>241</v>
       </c>
       <c r="E30" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1708,25 +1708,25 @@
         <v>16</v>
       </c>
       <c r="H30" t="n">
-        <v>1987.27651323329</v>
+        <v>1987.27651165142</v>
       </c>
       <c r="I30" t="n">
-        <v>1944.68443153655</v>
+        <v>1944.68444132775</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.72902505123359</v>
+        <v>-8.72902336659835</v>
       </c>
       <c r="K30" t="n">
-        <v>8.72902505123359</v>
+        <v>8.72902336659835</v>
       </c>
       <c r="L30" t="n">
-        <v>0.017017042434662</v>
+        <v>0.0167848133451827</v>
       </c>
       <c r="M30" t="n">
-        <v>0.026278186354253</v>
+        <v>0.0261872806679204</v>
       </c>
       <c r="N30" t="n">
-        <v>0.607020952834047</v>
+        <v>0.61103625017692</v>
       </c>
     </row>
     <row r="31">
@@ -1743,7 +1743,7 @@
         <v>241</v>
       </c>
       <c r="E31" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1764,13 +1764,13 @@
         <v>11.49142692762</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0285887434226135</v>
+        <v>0.0286114840523237</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0558500672080652</v>
+        <v>0.0558127312547028</v>
       </c>
       <c r="N31" t="n">
-        <v>0.407348704592926</v>
+        <v>0.409257453909081</v>
       </c>
     </row>
   </sheetData>
